--- a/students.xlsx
+++ b/students.xlsx
@@ -5,7 +5,7 @@
   <workbookPr codeName="ThisWorkbook" defaultThemeVersion="153222"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\LENOVO\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\LENOVO\PycharmProjects\WelcomeScreen\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="127" uniqueCount="126">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="261" uniqueCount="258">
   <si>
     <t>Name</t>
   </si>
@@ -397,6 +397,402 @@
   </si>
   <si>
     <t>sr_numer</t>
+  </si>
+  <si>
+    <t>ANSHUMAN PANDEY</t>
+  </si>
+  <si>
+    <t>38900</t>
+  </si>
+  <si>
+    <t>ANUJ KUMAR YADAV</t>
+  </si>
+  <si>
+    <t>37496</t>
+  </si>
+  <si>
+    <t>AYUSH KUMAR SINGH</t>
+  </si>
+  <si>
+    <t>37543</t>
+  </si>
+  <si>
+    <t>DHEERAJ KUMAR</t>
+  </si>
+  <si>
+    <t>37462</t>
+  </si>
+  <si>
+    <t>DIVYANSHU SINGH</t>
+  </si>
+  <si>
+    <t>37463</t>
+  </si>
+  <si>
+    <t>MITHLESH KUMAR</t>
+  </si>
+  <si>
+    <t>38257</t>
+  </si>
+  <si>
+    <t>NIKHIL PANDEY</t>
+  </si>
+  <si>
+    <t>37541</t>
+  </si>
+  <si>
+    <t>AJAY KUMAR</t>
+  </si>
+  <si>
+    <t>38927</t>
+  </si>
+  <si>
+    <t>RAGHUVANSH SINGH</t>
+  </si>
+  <si>
+    <t>37464</t>
+  </si>
+  <si>
+    <t>SACHIN KUMAR GUPTA</t>
+  </si>
+  <si>
+    <t>37602</t>
+  </si>
+  <si>
+    <t>SHASHIKANT</t>
+  </si>
+  <si>
+    <t>38252</t>
+  </si>
+  <si>
+    <t>SHIVAM KUMAR YADAV</t>
+  </si>
+  <si>
+    <t>38918</t>
+  </si>
+  <si>
+    <t>AMRITA SINGH</t>
+  </si>
+  <si>
+    <t>37471</t>
+  </si>
+  <si>
+    <t>ANJALI MAURYA</t>
+  </si>
+  <si>
+    <t>38268</t>
+  </si>
+  <si>
+    <t>ANSHIKA SHARMA</t>
+  </si>
+  <si>
+    <t>37627</t>
+  </si>
+  <si>
+    <t>ANSHIKA YADAV</t>
+  </si>
+  <si>
+    <t>37477</t>
+  </si>
+  <si>
+    <t>JYOTI SINGH</t>
+  </si>
+  <si>
+    <t>37518</t>
+  </si>
+  <si>
+    <t>PREETI KUMARI</t>
+  </si>
+  <si>
+    <t>37674</t>
+  </si>
+  <si>
+    <t>RAKHI RAI</t>
+  </si>
+  <si>
+    <t>37683</t>
+  </si>
+  <si>
+    <t>SANIYA KHATOON</t>
+  </si>
+  <si>
+    <t>37629</t>
+  </si>
+  <si>
+    <t>SARSWATI KUMARI</t>
+  </si>
+  <si>
+    <t>37667</t>
+  </si>
+  <si>
+    <t>SHIKSHA RAJPOOT</t>
+  </si>
+  <si>
+    <t>37553</t>
+  </si>
+  <si>
+    <t>SHREYA SINGH</t>
+  </si>
+  <si>
+    <t>37472</t>
+  </si>
+  <si>
+    <t>SONALI YADAV</t>
+  </si>
+  <si>
+    <t>37657</t>
+  </si>
+  <si>
+    <t>37526</t>
+  </si>
+  <si>
+    <t>AKARSH OJHA</t>
+  </si>
+  <si>
+    <t>38259</t>
+  </si>
+  <si>
+    <t>NAMAN SINGH</t>
+  </si>
+  <si>
+    <t>37509</t>
+  </si>
+  <si>
+    <t>SAMRAT KARMKAR</t>
+  </si>
+  <si>
+    <t>37655</t>
+  </si>
+  <si>
+    <t>SHUBHAM KUMAR</t>
+  </si>
+  <si>
+    <t>37547</t>
+  </si>
+  <si>
+    <t>ADITYA GUPTA</t>
+  </si>
+  <si>
+    <t>37646</t>
+  </si>
+  <si>
+    <t>ADITYA KUMAR</t>
+  </si>
+  <si>
+    <t>37461</t>
+  </si>
+  <si>
+    <t>37581</t>
+  </si>
+  <si>
+    <t>ANU KUMARI YADAV</t>
+  </si>
+  <si>
+    <t>37633</t>
+  </si>
+  <si>
+    <t>HARSHITA SINGH</t>
+  </si>
+  <si>
+    <t>38920</t>
+  </si>
+  <si>
+    <t>NEHA KUMARI</t>
+  </si>
+  <si>
+    <t>37671</t>
+  </si>
+  <si>
+    <t>RIYA SAROJ</t>
+  </si>
+  <si>
+    <t>37687</t>
+  </si>
+  <si>
+    <t>SHEETAL SINGH</t>
+  </si>
+  <si>
+    <t>37690</t>
+  </si>
+  <si>
+    <t>SHRUTI TIWARI</t>
+  </si>
+  <si>
+    <t>38251</t>
+  </si>
+  <si>
+    <t>ADITYA KUMAR KANNAUJIYA</t>
+  </si>
+  <si>
+    <t>39566</t>
+  </si>
+  <si>
+    <t>SUMIT</t>
+  </si>
+  <si>
+    <t>39427</t>
+  </si>
+  <si>
+    <t>TAUFEEQ ALAM</t>
+  </si>
+  <si>
+    <t>39546</t>
+  </si>
+  <si>
+    <t>SATYAM MEHTA</t>
+  </si>
+  <si>
+    <t>39478</t>
+  </si>
+  <si>
+    <t>SHASHI KUMAR</t>
+  </si>
+  <si>
+    <t>39569</t>
+  </si>
+  <si>
+    <t>ALOK KUMAR</t>
+  </si>
+  <si>
+    <t>39533</t>
+  </si>
+  <si>
+    <t>AVESH ANSARI</t>
+  </si>
+  <si>
+    <t>39471</t>
+  </si>
+  <si>
+    <t>AVINASH CHANDRA SHARMA</t>
+  </si>
+  <si>
+    <t>39535</t>
+  </si>
+  <si>
+    <t>BHAVESH PAL</t>
+  </si>
+  <si>
+    <t>39472</t>
+  </si>
+  <si>
+    <t>PRITAM KUMAR-II</t>
+  </si>
+  <si>
+    <t>39538</t>
+  </si>
+  <si>
+    <t>ANJALI JHA</t>
+  </si>
+  <si>
+    <t>39446</t>
+  </si>
+  <si>
+    <t>ANSHU KUMARI</t>
+  </si>
+  <si>
+    <t>39450</t>
+  </si>
+  <si>
+    <t>DIVYA</t>
+  </si>
+  <si>
+    <t>39441</t>
+  </si>
+  <si>
+    <t>DIVYA SONI</t>
+  </si>
+  <si>
+    <t>39455</t>
+  </si>
+  <si>
+    <t>KRITIKA SRIVASTAVA</t>
+  </si>
+  <si>
+    <t>39443</t>
+  </si>
+  <si>
+    <t>KHUSHI PANDEY</t>
+  </si>
+  <si>
+    <t>39465</t>
+  </si>
+  <si>
+    <t>PRIYANSHU VERMA</t>
+  </si>
+  <si>
+    <t>39501</t>
+  </si>
+  <si>
+    <t>RENU YADAV</t>
+  </si>
+  <si>
+    <t>39507</t>
+  </si>
+  <si>
+    <t>PRADEEP KUMAR GUPTA</t>
+  </si>
+  <si>
+    <t>40140</t>
+  </si>
+  <si>
+    <t>ARVIND KUMAR</t>
+  </si>
+  <si>
+    <t>40122</t>
+  </si>
+  <si>
+    <t>PRITI</t>
+  </si>
+  <si>
+    <t>2568948</t>
+  </si>
+  <si>
+    <t>SEEMA YADAV</t>
+  </si>
+  <si>
+    <t>2568949</t>
+  </si>
+  <si>
+    <t>ANURAG KUMAR</t>
+  </si>
+  <si>
+    <t>2568950</t>
+  </si>
+  <si>
+    <t>DHEERAJ PANDEY</t>
+  </si>
+  <si>
+    <t>2568951</t>
+  </si>
+  <si>
+    <t>UJJWAL KUMAR</t>
+  </si>
+  <si>
+    <t>2568952</t>
+  </si>
+  <si>
+    <t>ARYAN JAISWAL</t>
+  </si>
+  <si>
+    <t>2568953</t>
+  </si>
+  <si>
+    <t>RANJAN KUMAR</t>
+  </si>
+  <si>
+    <t>2568969</t>
+  </si>
+  <si>
+    <t>RAMJANM</t>
+  </si>
+  <si>
+    <t>2569027</t>
+  </si>
+  <si>
+    <t>POOJA KUMARI</t>
+  </si>
+  <si>
+    <t>2569036</t>
   </si>
 </sst>
 </file>
@@ -826,7 +1222,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:B64"/>
+  <dimension ref="A1:B131"/>
   <sheetFormatPr defaultRowHeight="14" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="2" width="31.453125" customWidth="1"/>
@@ -1344,6 +1740,542 @@
         <v>123</v>
       </c>
     </row>
+    <row r="65" spans="1:2" ht="17" x14ac:dyDescent="0.4">
+      <c r="A65" s="2" t="s">
+        <v>126</v>
+      </c>
+      <c r="B65" s="1" t="s">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="66" spans="1:2" ht="17" x14ac:dyDescent="0.4">
+      <c r="A66" s="2" t="s">
+        <v>128</v>
+      </c>
+      <c r="B66" s="1" t="s">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="67" spans="1:2" ht="17" x14ac:dyDescent="0.4">
+      <c r="A67" s="2" t="s">
+        <v>130</v>
+      </c>
+      <c r="B67" s="1" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="68" spans="1:2" ht="17" x14ac:dyDescent="0.4">
+      <c r="A68" s="2" t="s">
+        <v>132</v>
+      </c>
+      <c r="B68" s="1" t="s">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="69" spans="1:2" ht="17" x14ac:dyDescent="0.4">
+      <c r="A69" s="2" t="s">
+        <v>134</v>
+      </c>
+      <c r="B69" s="1" t="s">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="70" spans="1:2" ht="17" x14ac:dyDescent="0.4">
+      <c r="A70" s="2" t="s">
+        <v>136</v>
+      </c>
+      <c r="B70" s="1" t="s">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="71" spans="1:2" ht="17" x14ac:dyDescent="0.4">
+      <c r="A71" s="2" t="s">
+        <v>138</v>
+      </c>
+      <c r="B71" s="1" t="s">
+        <v>139</v>
+      </c>
+    </row>
+    <row r="72" spans="1:2" ht="17" x14ac:dyDescent="0.4">
+      <c r="A72" s="2" t="s">
+        <v>140</v>
+      </c>
+      <c r="B72" s="1" t="s">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="73" spans="1:2" ht="17" x14ac:dyDescent="0.4">
+      <c r="A73" s="2" t="s">
+        <v>142</v>
+      </c>
+      <c r="B73" s="1" t="s">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="74" spans="1:2" ht="17" x14ac:dyDescent="0.4">
+      <c r="A74" s="2" t="s">
+        <v>144</v>
+      </c>
+      <c r="B74" s="1" t="s">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="75" spans="1:2" ht="17" x14ac:dyDescent="0.4">
+      <c r="A75" s="2" t="s">
+        <v>146</v>
+      </c>
+      <c r="B75" s="1" t="s">
+        <v>147</v>
+      </c>
+    </row>
+    <row r="76" spans="1:2" ht="17" x14ac:dyDescent="0.4">
+      <c r="A76" s="2" t="s">
+        <v>148</v>
+      </c>
+      <c r="B76" s="1" t="s">
+        <v>149</v>
+      </c>
+    </row>
+    <row r="77" spans="1:2" ht="17" x14ac:dyDescent="0.4">
+      <c r="A77" s="2" t="s">
+        <v>150</v>
+      </c>
+      <c r="B77" s="1" t="s">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="78" spans="1:2" ht="17" x14ac:dyDescent="0.4">
+      <c r="A78" s="2" t="s">
+        <v>152</v>
+      </c>
+      <c r="B78" s="1" t="s">
+        <v>153</v>
+      </c>
+    </row>
+    <row r="79" spans="1:2" ht="17" x14ac:dyDescent="0.4">
+      <c r="A79" s="2" t="s">
+        <v>154</v>
+      </c>
+      <c r="B79" s="1" t="s">
+        <v>155</v>
+      </c>
+    </row>
+    <row r="80" spans="1:2" ht="17" x14ac:dyDescent="0.4">
+      <c r="A80" s="2" t="s">
+        <v>156</v>
+      </c>
+      <c r="B80" s="1" t="s">
+        <v>157</v>
+      </c>
+    </row>
+    <row r="81" spans="1:2" ht="17" x14ac:dyDescent="0.4">
+      <c r="A81" s="2" t="s">
+        <v>158</v>
+      </c>
+      <c r="B81" s="1" t="s">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="82" spans="1:2" ht="17" x14ac:dyDescent="0.4">
+      <c r="A82" s="2" t="s">
+        <v>160</v>
+      </c>
+      <c r="B82" s="1" t="s">
+        <v>161</v>
+      </c>
+    </row>
+    <row r="83" spans="1:2" ht="17" x14ac:dyDescent="0.4">
+      <c r="A83" s="2" t="s">
+        <v>162</v>
+      </c>
+      <c r="B83" s="1" t="s">
+        <v>163</v>
+      </c>
+    </row>
+    <row r="84" spans="1:2" ht="17" x14ac:dyDescent="0.4">
+      <c r="A84" s="2" t="s">
+        <v>164</v>
+      </c>
+      <c r="B84" s="1" t="s">
+        <v>165</v>
+      </c>
+    </row>
+    <row r="85" spans="1:2" ht="17" x14ac:dyDescent="0.4">
+      <c r="A85" s="2" t="s">
+        <v>166</v>
+      </c>
+      <c r="B85" s="1" t="s">
+        <v>167</v>
+      </c>
+    </row>
+    <row r="86" spans="1:2" ht="17" x14ac:dyDescent="0.4">
+      <c r="A86" s="2" t="s">
+        <v>168</v>
+      </c>
+      <c r="B86" s="1" t="s">
+        <v>169</v>
+      </c>
+    </row>
+    <row r="87" spans="1:2" ht="17" x14ac:dyDescent="0.4">
+      <c r="A87" s="2" t="s">
+        <v>170</v>
+      </c>
+      <c r="B87" s="1" t="s">
+        <v>171</v>
+      </c>
+    </row>
+    <row r="88" spans="1:2" ht="17" x14ac:dyDescent="0.4">
+      <c r="A88" s="2" t="s">
+        <v>172</v>
+      </c>
+      <c r="B88" s="1" t="s">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="89" spans="1:2" ht="17" x14ac:dyDescent="0.4">
+      <c r="A89" s="2" t="s">
+        <v>108</v>
+      </c>
+      <c r="B89" s="1" t="s">
+        <v>174</v>
+      </c>
+    </row>
+    <row r="90" spans="1:2" ht="17" x14ac:dyDescent="0.4">
+      <c r="A90" s="2" t="s">
+        <v>175</v>
+      </c>
+      <c r="B90" s="1" t="s">
+        <v>176</v>
+      </c>
+    </row>
+    <row r="91" spans="1:2" ht="17" x14ac:dyDescent="0.4">
+      <c r="A91" s="2" t="s">
+        <v>177</v>
+      </c>
+      <c r="B91" s="1" t="s">
+        <v>178</v>
+      </c>
+    </row>
+    <row r="92" spans="1:2" ht="17" x14ac:dyDescent="0.4">
+      <c r="A92" s="2" t="s">
+        <v>179</v>
+      </c>
+      <c r="B92" s="1" t="s">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="93" spans="1:2" ht="17" x14ac:dyDescent="0.4">
+      <c r="A93" s="2" t="s">
+        <v>181</v>
+      </c>
+      <c r="B93" s="1" t="s">
+        <v>182</v>
+      </c>
+    </row>
+    <row r="94" spans="1:2" ht="17" x14ac:dyDescent="0.4">
+      <c r="A94" s="2" t="s">
+        <v>183</v>
+      </c>
+      <c r="B94" s="1" t="s">
+        <v>184</v>
+      </c>
+    </row>
+    <row r="95" spans="1:2" ht="17" x14ac:dyDescent="0.4">
+      <c r="A95" s="2" t="s">
+        <v>185</v>
+      </c>
+      <c r="B95" s="1" t="s">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="96" spans="1:2" ht="17" x14ac:dyDescent="0.4">
+      <c r="A96" s="2" t="s">
+        <v>185</v>
+      </c>
+      <c r="B96" s="1" t="s">
+        <v>187</v>
+      </c>
+    </row>
+    <row r="97" spans="1:2" ht="17" x14ac:dyDescent="0.4">
+      <c r="A97" s="2" t="s">
+        <v>188</v>
+      </c>
+      <c r="B97" s="1" t="s">
+        <v>189</v>
+      </c>
+    </row>
+    <row r="98" spans="1:2" ht="17" x14ac:dyDescent="0.4">
+      <c r="A98" s="2" t="s">
+        <v>190</v>
+      </c>
+      <c r="B98" s="1" t="s">
+        <v>191</v>
+      </c>
+    </row>
+    <row r="99" spans="1:2" ht="17" x14ac:dyDescent="0.4">
+      <c r="A99" s="2" t="s">
+        <v>192</v>
+      </c>
+      <c r="B99" s="1" t="s">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="100" spans="1:2" ht="17" x14ac:dyDescent="0.4">
+      <c r="A100" s="2" t="s">
+        <v>194</v>
+      </c>
+      <c r="B100" s="1" t="s">
+        <v>195</v>
+      </c>
+    </row>
+    <row r="101" spans="1:2" ht="17" x14ac:dyDescent="0.4">
+      <c r="A101" s="2" t="s">
+        <v>196</v>
+      </c>
+      <c r="B101" s="1" t="s">
+        <v>197</v>
+      </c>
+    </row>
+    <row r="102" spans="1:2" ht="17" x14ac:dyDescent="0.4">
+      <c r="A102" s="2" t="s">
+        <v>198</v>
+      </c>
+      <c r="B102" s="1" t="s">
+        <v>199</v>
+      </c>
+    </row>
+    <row r="103" spans="1:2" ht="17" x14ac:dyDescent="0.4">
+      <c r="A103" s="2" t="s">
+        <v>200</v>
+      </c>
+      <c r="B103" s="1" t="s">
+        <v>201</v>
+      </c>
+    </row>
+    <row r="104" spans="1:2" ht="17" x14ac:dyDescent="0.4">
+      <c r="A104" s="2" t="s">
+        <v>202</v>
+      </c>
+      <c r="B104" s="1" t="s">
+        <v>203</v>
+      </c>
+    </row>
+    <row r="105" spans="1:2" ht="17" x14ac:dyDescent="0.4">
+      <c r="A105" s="2" t="s">
+        <v>204</v>
+      </c>
+      <c r="B105" s="1" t="s">
+        <v>205</v>
+      </c>
+    </row>
+    <row r="106" spans="1:2" ht="17" x14ac:dyDescent="0.4">
+      <c r="A106" s="2" t="s">
+        <v>206</v>
+      </c>
+      <c r="B106" s="1" t="s">
+        <v>207</v>
+      </c>
+    </row>
+    <row r="107" spans="1:2" ht="17" x14ac:dyDescent="0.4">
+      <c r="A107" s="2" t="s">
+        <v>208</v>
+      </c>
+      <c r="B107" s="1" t="s">
+        <v>209</v>
+      </c>
+    </row>
+    <row r="108" spans="1:2" ht="17" x14ac:dyDescent="0.4">
+      <c r="A108" s="2" t="s">
+        <v>210</v>
+      </c>
+      <c r="B108" s="1" t="s">
+        <v>211</v>
+      </c>
+    </row>
+    <row r="109" spans="1:2" ht="17" x14ac:dyDescent="0.4">
+      <c r="A109" s="2" t="s">
+        <v>212</v>
+      </c>
+      <c r="B109" s="1" t="s">
+        <v>213</v>
+      </c>
+    </row>
+    <row r="110" spans="1:2" ht="17" x14ac:dyDescent="0.4">
+      <c r="A110" s="2" t="s">
+        <v>214</v>
+      </c>
+      <c r="B110" s="1" t="s">
+        <v>215</v>
+      </c>
+    </row>
+    <row r="111" spans="1:2" ht="17" x14ac:dyDescent="0.4">
+      <c r="A111" s="2" t="s">
+        <v>216</v>
+      </c>
+      <c r="B111" s="1" t="s">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="112" spans="1:2" ht="17" x14ac:dyDescent="0.4">
+      <c r="A112" s="2" t="s">
+        <v>218</v>
+      </c>
+      <c r="B112" s="1" t="s">
+        <v>219</v>
+      </c>
+    </row>
+    <row r="113" spans="1:2" ht="17" x14ac:dyDescent="0.4">
+      <c r="A113" s="2" t="s">
+        <v>220</v>
+      </c>
+      <c r="B113" s="1" t="s">
+        <v>221</v>
+      </c>
+    </row>
+    <row r="114" spans="1:2" ht="17" x14ac:dyDescent="0.4">
+      <c r="A114" s="2" t="s">
+        <v>222</v>
+      </c>
+      <c r="B114" s="1" t="s">
+        <v>223</v>
+      </c>
+    </row>
+    <row r="115" spans="1:2" ht="17" x14ac:dyDescent="0.4">
+      <c r="A115" s="2" t="s">
+        <v>224</v>
+      </c>
+      <c r="B115" s="1" t="s">
+        <v>225</v>
+      </c>
+    </row>
+    <row r="116" spans="1:2" ht="17" x14ac:dyDescent="0.4">
+      <c r="A116" s="2" t="s">
+        <v>226</v>
+      </c>
+      <c r="B116" s="1" t="s">
+        <v>227</v>
+      </c>
+    </row>
+    <row r="117" spans="1:2" ht="17" x14ac:dyDescent="0.4">
+      <c r="A117" s="2" t="s">
+        <v>228</v>
+      </c>
+      <c r="B117" s="1" t="s">
+        <v>229</v>
+      </c>
+    </row>
+    <row r="118" spans="1:2" ht="17" x14ac:dyDescent="0.4">
+      <c r="A118" s="2" t="s">
+        <v>230</v>
+      </c>
+      <c r="B118" s="1" t="s">
+        <v>231</v>
+      </c>
+    </row>
+    <row r="119" spans="1:2" ht="17" x14ac:dyDescent="0.4">
+      <c r="A119" s="2" t="s">
+        <v>232</v>
+      </c>
+      <c r="B119" s="1" t="s">
+        <v>233</v>
+      </c>
+    </row>
+    <row r="120" spans="1:2" ht="17" x14ac:dyDescent="0.4">
+      <c r="A120" s="2" t="s">
+        <v>234</v>
+      </c>
+      <c r="B120" s="1" t="s">
+        <v>235</v>
+      </c>
+    </row>
+    <row r="121" spans="1:2" ht="17" x14ac:dyDescent="0.4">
+      <c r="A121" s="2" t="s">
+        <v>236</v>
+      </c>
+      <c r="B121" s="1" t="s">
+        <v>237</v>
+      </c>
+    </row>
+    <row r="122" spans="1:2" ht="17" x14ac:dyDescent="0.4">
+      <c r="A122" s="2" t="s">
+        <v>238</v>
+      </c>
+      <c r="B122" s="1" t="s">
+        <v>239</v>
+      </c>
+    </row>
+    <row r="123" spans="1:2" ht="17" x14ac:dyDescent="0.4">
+      <c r="A123" s="2" t="s">
+        <v>240</v>
+      </c>
+      <c r="B123" s="1" t="s">
+        <v>241</v>
+      </c>
+    </row>
+    <row r="124" spans="1:2" ht="17" x14ac:dyDescent="0.4">
+      <c r="A124" s="2" t="s">
+        <v>242</v>
+      </c>
+      <c r="B124" s="1" t="s">
+        <v>243</v>
+      </c>
+    </row>
+    <row r="125" spans="1:2" ht="17" x14ac:dyDescent="0.4">
+      <c r="A125" s="2" t="s">
+        <v>244</v>
+      </c>
+      <c r="B125" s="1" t="s">
+        <v>245</v>
+      </c>
+    </row>
+    <row r="126" spans="1:2" ht="17" x14ac:dyDescent="0.4">
+      <c r="A126" s="2" t="s">
+        <v>246</v>
+      </c>
+      <c r="B126" s="1" t="s">
+        <v>247</v>
+      </c>
+    </row>
+    <row r="127" spans="1:2" ht="17" x14ac:dyDescent="0.4">
+      <c r="A127" s="2" t="s">
+        <v>248</v>
+      </c>
+      <c r="B127" s="1" t="s">
+        <v>249</v>
+      </c>
+    </row>
+    <row r="128" spans="1:2" ht="17" x14ac:dyDescent="0.4">
+      <c r="A128" s="2" t="s">
+        <v>250</v>
+      </c>
+      <c r="B128" s="1" t="s">
+        <v>251</v>
+      </c>
+    </row>
+    <row r="129" spans="1:2" ht="17" x14ac:dyDescent="0.4">
+      <c r="A129" s="2" t="s">
+        <v>252</v>
+      </c>
+      <c r="B129" s="1" t="s">
+        <v>253</v>
+      </c>
+    </row>
+    <row r="130" spans="1:2" ht="17" x14ac:dyDescent="0.4">
+      <c r="A130" s="2" t="s">
+        <v>254</v>
+      </c>
+      <c r="B130" s="1" t="s">
+        <v>255</v>
+      </c>
+    </row>
+    <row r="131" spans="1:2" ht="17" x14ac:dyDescent="0.4">
+      <c r="A131" s="2" t="s">
+        <v>256</v>
+      </c>
+      <c r="B131" s="1" t="s">
+        <v>257</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <headerFooter alignWithMargins="0"/>
